--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2798,7 +2798,7 @@
         <v>136923463</v>
       </c>
       <c r="B22" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136923464</v>
       </c>
       <c r="B23" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136923465</v>
       </c>
       <c r="B24" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>136923494</v>
       </c>
       <c r="B42" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>136923491</v>
       </c>
       <c r="B161" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>136923492</v>
       </c>
       <c r="B162" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>136923493</v>
       </c>
       <c r="B191" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>136923496</v>
       </c>
       <c r="B192" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>136923495</v>
       </c>
       <c r="B283" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
